--- a/docs/qa_run_2026-09-30/FreedomBot_UI_test_results_2026-09-30.xlsx
+++ b/docs/qa_run_2026-09-30/FreedomBot_UI_test_results_2026-09-30.xlsx
@@ -3691,23 +3691,31 @@
           <t>M05-08</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Chat indirect probes were refused, but Viewer and Employee can read finance credit amounts and customers on the Approvals page.</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr"/>
+          <t>Retest after fix: Viewer and Employee see no finance actions on the Approvals page (API returns 404 for a direct link); Finance and Approver still see them.</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M05-08_viewer.png</t>
+        </is>
+      </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
           <t>BUG-04</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Chat indirect probes were refused, but Viewer and Employee can read finance credit amounts and customers on the Approvals page.</t>
+        </is>
+      </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
           <t>M05 Role-aware access</t>
@@ -4152,14 +4160,14 @@
           <t>M06-05</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Plain chat email send was routed to "general", where the send tool is missing; bot said "submitted for approval" three times with nothing queued. Works only when routed to sales.</t>
+          <t>Retest after fix: 3 of 4 plain email requests routed to sales and queued PENDING_APPROVAL. The 4th, with no address or body, was drafted and the bot asked to send; no false approval claim.</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr"/>
@@ -4168,7 +4176,11 @@
           <t>BUG-03</t>
         </is>
       </c>
-      <c r="F106" s="8" t="inlineStr"/>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Plain chat email send was routed to "general", where the send tool is missing; bot said "submitted for approval" three times with nothing queued. Works only when routed to sales.</t>
+        </is>
+      </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
           <t>M06 Advise/Draft/Approve/Auto + audit</t>
@@ -4888,14 +4900,14 @@
           <t>M07-13</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Bot was willing to create a CRM contact for a 9-year-old and only asked for an email.</t>
+          <t>Retest after fix: platform refused before the model ran; no CRM tool called. Writes carrying child data are also denied by policy.</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr"/>
@@ -4906,7 +4918,7 @@
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>Not created only because no email was given.</t>
+          <t>Originally failed: Bot was willing to create a CRM contact for a 9-year-old and only asked for an email.</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
@@ -5075,14 +5087,14 @@
           <t>M07-20</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Audit MEMORY_READ rows store the raw question, including the fake SSN and fake MRN.</t>
+          <t>Retest after fix: new audit rows hold no SSN, MRN, DOB or diagnosis text; chat history redacts identifiers. Two rows from the first run remain (audit is append-only).</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr"/>
@@ -5091,7 +5103,11 @@
           <t>BUG-05</t>
         </is>
       </c>
-      <c r="F141" s="8" t="inlineStr"/>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Audit MEMORY_READ rows store the raw question, including the fake SSN and fake MRN.</t>
+        </is>
+      </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
           <t>M07 Licensed judgment + regulated data</t>
@@ -5906,23 +5922,31 @@
           <t>M09-11</t>
         </is>
       </c>
-      <c r="B172" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Alerts are hard-coded Acme payroll text, not derived from client data.</t>
-        </is>
-      </c>
-      <c r="D172" s="8" t="inlineStr"/>
+          <t>Retest after fix: alerts come from workspace data — 3 finance approvals waiting a median 4 days, and one question asked by 3 people — each showing its evidence.</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M09_insights.png</t>
+        </is>
+      </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
           <t>BUG-18</t>
         </is>
       </c>
-      <c r="F172" s="8" t="inlineStr"/>
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Alerts are hard-coded Acme payroll text, not derived from client data.</t>
+        </is>
+      </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
           <t>M09 Inefficiency alerts v1</t>
@@ -5960,23 +5984,31 @@
           <t>M09-13</t>
         </is>
       </c>
-      <c r="B174" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>No mechanism to surface a new alert.</t>
-        </is>
-      </c>
-      <c r="D174" s="8" t="inlineStr"/>
+          <t>Retest after fix: 'Scan now' (and an hourly rescan) raised new alerts once the patterns appeared; at most 2 current, the rest held.</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M09_insights.png</t>
+        </is>
+      </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
           <t>BUG-18</t>
         </is>
       </c>
-      <c r="F174" s="8" t="inlineStr"/>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: No mechanism to surface a new alert.</t>
+        </is>
+      </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
           <t>M09 Inefficiency alerts v1</t>
@@ -5989,14 +6021,14 @@
           <t>M09-14</t>
         </is>
       </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Alerts have no access areas; Employee sees payroll alerts.</t>
+          <t>Retest after fix: the finance approval-delay alert shows for Finance but not for Employee.</t>
         </is>
       </c>
       <c r="D175" s="8" t="inlineStr"/>
@@ -6005,7 +6037,11 @@
           <t>BUG-18</t>
         </is>
       </c>
-      <c r="F175" s="8" t="inlineStr"/>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Alerts have no access areas; Employee sees payroll alerts.</t>
+        </is>
+      </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
           <t>M09 Inefficiency alerts v1</t>
@@ -6251,23 +6287,31 @@
           <t>M10-04</t>
         </is>
       </c>
-      <c r="B185" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Input is single-line; Shift+Enter submits and newlines are stripped.</t>
-        </is>
-      </c>
-      <c r="D185" s="8" t="inlineStr"/>
+          <t>Retest after fix: text area; Shift+Enter added a line and the sent bubble kept both lines.</t>
+        </is>
+      </c>
+      <c r="D185" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M10-04_multiline.png</t>
+        </is>
+      </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
           <t>BUG-12</t>
         </is>
       </c>
-      <c r="F185" s="8" t="inlineStr"/>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Input is single-line; Shift+Enter submits and newlines are stripped.</t>
+        </is>
+      </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
           <t>M10 Default chat interface</t>
@@ -6911,23 +6955,31 @@
           <t>M11-08</t>
         </is>
       </c>
-      <c r="B209" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B209" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>Missing systems were filled with invented defaults (Workspace CRM, Workspace Email, n8n) instead of asking.</t>
-        </is>
-      </c>
-      <c r="D209" s="8" t="inlineStr"/>
+          <t>Retest after fix: no default systems invented; a missing systems answer becomes a question for the client.</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M11_setup_clarification.png</t>
+        </is>
+      </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
           <t>BUG-17</t>
         </is>
       </c>
-      <c r="F209" s="8" t="inlineStr"/>
+      <c r="F209" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Missing systems were filled with invented defaults (Workspace CRM, Workspace Email, n8n) instead of asking.</t>
+        </is>
+      </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
           <t>M11 Paid client handoff</t>
@@ -6940,14 +6992,14 @@
           <t>M11-09</t>
         </is>
       </c>
-      <c r="B210" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B210" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Missing permissions left blank with no prompt.</t>
+          <t>Retest after fix: missing permissions produce a 'who sees which areas' question (dropped once roles notes exist).</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr"/>
@@ -6956,7 +7008,11 @@
           <t>BUG-17</t>
         </is>
       </c>
-      <c r="F210" s="8" t="inlineStr"/>
+      <c r="F210" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Missing permissions left blank with no prompt.</t>
+        </is>
+      </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
           <t>M11 Paid client handoff</t>
@@ -6969,23 +7025,31 @@
           <t>M11-10</t>
         </is>
       </c>
-      <c r="B211" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B211" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>No prompt for missing authority information.</t>
-        </is>
-      </c>
-      <c r="D211" s="8" t="inlineStr"/>
+          <t>Retest after fix: 'Who may approve actions, and up to what limits?' listed under Needs clarification.</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M11_setup_clarification.png</t>
+        </is>
+      </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
           <t>BUG-17</t>
         </is>
       </c>
-      <c r="F211" s="8" t="inlineStr"/>
+      <c r="F211" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: No prompt for missing authority information.</t>
+        </is>
+      </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
           <t>M11 Paid client handoff</t>
@@ -7052,23 +7116,31 @@
           <t>M11-13</t>
         </is>
       </c>
-      <c r="B214" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B214" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Headcount 25 vs employees 40 not flagged.</t>
-        </is>
-      </c>
-      <c r="D214" s="8" t="inlineStr"/>
+          <t>Retest after fix: 'employee count is given differently (headcount = 25, employees = 40)' flagged.</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M11_setup_clarification.png</t>
+        </is>
+      </c>
       <c r="E214" s="8" t="inlineStr">
         <is>
           <t>BUG-17</t>
         </is>
       </c>
-      <c r="F214" s="8" t="inlineStr"/>
+      <c r="F214" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Headcount 25 vs employees 40 not flagged.</t>
+        </is>
+      </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
           <t>M11 Paid client handoff</t>
@@ -7206,14 +7278,14 @@
           <t>M11-19</t>
         </is>
       </c>
-      <c r="B220" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B220" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Assumption "AI can fully automate approvals" stored as APPROVED fact and quoted as "Fact:".</t>
+          <t>Retest after fix: the assumption is stored PENDING as unverified and the chat no longer quotes it as a fact.</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr"/>
@@ -7222,7 +7294,11 @@
           <t>BUG-16</t>
         </is>
       </c>
-      <c r="F220" s="8" t="inlineStr"/>
+      <c r="F220" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Assumption "AI can fully automate approvals" stored as APPROVED fact and quoted as "Fact:".</t>
+        </is>
+      </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
           <t>M11 Paid client handoff</t>
@@ -7551,14 +7627,14 @@
           <t>M12-12</t>
         </is>
       </c>
-      <c r="B233" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C233" s="8" t="inlineStr">
         <is>
-          <t>No way to remove a workflow/SOP.</t>
+          <t>Retest after fix: 'Invoice from job ticket' SOP removed; no longer listed or used.</t>
         </is>
       </c>
       <c r="D233" s="8" t="inlineStr"/>
@@ -7567,7 +7643,11 @@
           <t>BUG-14</t>
         </is>
       </c>
-      <c r="F233" s="8" t="inlineStr"/>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: No way to remove a workflow/SOP.</t>
+        </is>
+      </c>
       <c r="G233" s="8" t="inlineStr">
         <is>
           <t>M12 Configure first client</t>
@@ -7792,14 +7872,14 @@
           <t>M13-01</t>
         </is>
       </c>
-      <c r="B242" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B242" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Chat and memory isolation hold, but any client admin can read all clients' owner portfolio and edit another client's status.</t>
+          <t>Retest after fix: client admins get 403 on the owner view; chat and memory isolation hold.</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr"/>
@@ -7808,7 +7888,11 @@
           <t>BUG-01</t>
         </is>
       </c>
-      <c r="F242" s="8" t="inlineStr"/>
+      <c r="F242" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Chat and memory isolation hold, but any client admin can read all clients' owner portfolio and edit another client's status.</t>
+        </is>
+      </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
           <t>M13 Isolation &amp; launch acceptance</t>
@@ -8749,14 +8833,14 @@
           <t>M14-18</t>
         </is>
       </c>
-      <c r="B279" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B279" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C279" s="8" t="inlineStr">
         <is>
-          <t>Two identical submissions created two tickets.</t>
+          <t>Retest after fix: second identical submission merged into the open ticket with a notice.</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr"/>
@@ -8765,7 +8849,11 @@
           <t>BUG-23</t>
         </is>
       </c>
-      <c r="F279" s="8" t="inlineStr"/>
+      <c r="F279" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: Two identical submissions created two tickets.</t>
+        </is>
+      </c>
       <c r="G279" s="8" t="inlineStr">
         <is>
           <t>M14 Routine support to Cepoch</t>
@@ -9323,17 +9411,21 @@
           <t>M15-20</t>
         </is>
       </c>
-      <c r="B301" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B301" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C301" s="8" t="inlineStr">
         <is>
-          <t>Operator and viewer get 403, but Globex's admin read all clients' portfolio and overwrote Acme's status.</t>
-        </is>
-      </c>
-      <c r="D301" s="8" t="inlineStr"/>
+          <t>Retest after fix: Globex admin gets 403 reading or changing the portfolio; Owner tab hidden for client admins; Jeanne (platform owner) sees 3 clients.</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M15-20_owner_jeanne.png</t>
+        </is>
+      </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
           <t>BUG-01</t>
@@ -9341,7 +9433,7 @@
       </c>
       <c r="F301" s="8" t="inlineStr">
         <is>
-          <t>Critical.</t>
+          <t>Originally failed: Operator and viewer get 403, but Globex's admin read all clients' portfolio and overwrote Acme's status.</t>
         </is>
       </c>
       <c r="G301" s="8" t="inlineStr">
@@ -10051,14 +10143,14 @@
           <t>M17-08</t>
         </is>
       </c>
-      <c r="B329" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B329" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C329" s="8" t="inlineStr">
         <is>
-          <t>$0 price accepted and a $0 quote produced.</t>
+          <t>Retest after fix: $0 price refused with a clear message.</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr"/>
@@ -10067,7 +10159,11 @@
           <t>BUG-10</t>
         </is>
       </c>
-      <c r="F329" s="8" t="inlineStr"/>
+      <c r="F329" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: $0 price accepted and a $0 quote produced.</t>
+        </is>
+      </c>
       <c r="G329" s="8" t="inlineStr">
         <is>
           <t>M17 Consult pricing math</t>
@@ -10629,23 +10725,31 @@
           <t>M18-10</t>
         </is>
       </c>
-      <c r="B351" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B351" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C351" s="8" t="inlineStr">
         <is>
-          <t>No before/after difference shown; chat cannot read baselines.</t>
-        </is>
-      </c>
-      <c r="D351" s="8" t="inlineStr"/>
+          <t>Retest after fix: cycle time 12→7 shows '-5 days (-41.7%)'.</t>
+        </is>
+      </c>
+      <c r="D351" s="8" t="inlineStr">
+        <is>
+          <t>screenshots/retest_M09_insights.png</t>
+        </is>
+      </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
           <t>BUG-19</t>
         </is>
       </c>
-      <c r="F351" s="8" t="inlineStr"/>
+      <c r="F351" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: No before/after difference shown; chat cannot read baselines.</t>
+        </is>
+      </c>
       <c r="G351" s="8" t="inlineStr">
         <is>
           <t>M18 Baseline vs after</t>
@@ -10658,14 +10762,14 @@
           <t>M18-11</t>
         </is>
       </c>
-      <c r="B352" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B352" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C352" s="8" t="inlineStr">
         <is>
-          <t>No difference shown.</t>
+          <t>Retest after fix: manual hours 80→35 shows '-45 hours (-56.2%)'.</t>
         </is>
       </c>
       <c r="D352" s="8" t="inlineStr"/>
@@ -10674,7 +10778,11 @@
           <t>BUG-19</t>
         </is>
       </c>
-      <c r="F352" s="8" t="inlineStr"/>
+      <c r="F352" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: No difference shown.</t>
+        </is>
+      </c>
       <c r="G352" s="8" t="inlineStr">
         <is>
           <t>M18 Baseline vs after</t>
@@ -10791,14 +10899,14 @@
           <t>M18-16</t>
         </is>
       </c>
-      <c r="B357" s="11" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="B357" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="C357" s="8" t="inlineStr">
         <is>
-          <t>"-5" and "abc" accepted.</t>
+          <t>Retest after fix: '-5' and 'abc' refused with clear messages.</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr"/>
@@ -10807,7 +10915,11 @@
           <t>BUG-19</t>
         </is>
       </c>
-      <c r="F357" s="8" t="inlineStr"/>
+      <c r="F357" s="8" t="inlineStr">
+        <is>
+          <t>Originally failed: "-5" and "abc" accepted.</t>
+        </is>
+      </c>
       <c r="G357" s="8" t="inlineStr">
         <is>
           <t>M18 Baseline vs after</t>
@@ -11536,7 +11648,7 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G2" s="8">
@@ -11608,7 +11720,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Partly fixed 2026-09-30 (email routing + false-claim check)</t>
         </is>
       </c>
       <c r="G4" s="8">
@@ -11644,7 +11756,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G5" s="8">
@@ -11680,7 +11792,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G6" s="8">
@@ -11860,7 +11972,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G11" s="8">
@@ -11932,7 +12044,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G13" s="8">
@@ -12076,7 +12188,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G17" s="8">
@@ -12112,7 +12224,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G18" s="8">
@@ -12148,7 +12260,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G19" s="8">
@@ -12184,7 +12296,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G20" s="8">
@@ -12292,7 +12404,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G23" s="8">
@@ -12328,7 +12440,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed 2026-09-30</t>
         </is>
       </c>
       <c r="G24" s="8">
@@ -12364,7 +12476,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Partly fixed 2026-09-30 (owner view hidden from client admins)</t>
         </is>
       </c>
       <c r="G25" s="8">
